--- a/api/templates/result_notifications/fr.xlsx
+++ b/api/templates/result_notifications/fr.xlsx
@@ -1,32 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11207"/>
-  <workbookPr defaultThemeVersion="202300"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/harshthakkar/Desktop/Projects/aspect/api/templates/result_notifications/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{536D8109-AFA5-6749-B9FE-151C37F665A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
+  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" activeTab="1"/>
   </bookViews>
   <sheets>
-    <sheet name="SMS" sheetId="1" r:id="rId1"/>
-    <sheet name="Email" sheetId="2" r:id="rId2"/>
+    <sheet sheetId="1" name="SMS" state="visible" r:id="rId4"/>
+    <sheet sheetId="2" name="Email" state="visible" r:id="rId5"/>
   </sheets>
-  <calcPr calcId="0" iterateDelta="1E-4"/>
-  <extLst>
-    <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
-      <loext:extCalcPr stringRefSyntax="ExcelA1"/>
-    </ext>
-  </extLst>
+  <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="40">
   <si>
     <t>SMS Notifications</t>
   </si>
@@ -64,6 +53,9 @@
     <t>Device</t>
   </si>
   <si>
+    <t>Site</t>
+  </si>
+  <si>
     <t>Patient ID</t>
   </si>
   <si>
@@ -94,6 +86,9 @@
     <t>&lt;device&gt;</t>
   </si>
   <si>
+    <t>&lt;siteName&gt;</t>
+  </si>
+  <si>
     <t>&lt;patientId&gt;</t>
   </si>
   <si>
@@ -106,6 +101,33 @@
     <t>&lt;resultText&gt;</t>
   </si>
   <si>
+    <t>Notifications par e-mail</t>
+  </si>
+  <si>
+    <t>Destinataire</t>
+  </si>
+  <si>
+    <t>Messagerie électronique</t>
+  </si>
+  <si>
+    <t>Objet</t>
+  </si>
+  <si>
+    <t>Corps</t>
+  </si>
+  <si>
+    <t>Envoyé le</t>
+  </si>
+  <si>
+    <t>Appareil</t>
+  </si>
+  <si>
+    <t>ID de l’échantillon</t>
+  </si>
+  <si>
+    <t>Texte du résultat</t>
+  </si>
+  <si>
     <t>&lt;email&gt;</t>
   </si>
   <si>
@@ -113,88 +135,54 @@
   </si>
   <si>
     <t>&lt;body&gt;</t>
-  </si>
-  <si>
-    <t>Notifications par e-mail</t>
-  </si>
-  <si>
-    <t>Destinataire</t>
-  </si>
-  <si>
-    <t>Messagerie électronique</t>
-  </si>
-  <si>
-    <t>Objet</t>
-  </si>
-  <si>
-    <t>Corps</t>
-  </si>
-  <si>
-    <t>Envoyé le</t>
-  </si>
-  <si>
-    <t>Appareil</t>
-  </si>
-  <si>
-    <t>ID de l’échantillon</t>
-  </si>
-  <si>
-    <t>Texte du résultat</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd\ hh:mm"/>
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd hh:mm"/>
     <numFmt numFmtId="165" formatCode="m/d/yyyy"/>
   </numFmts>
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
-      <sz val="12"/>
-      <color rgb="FF000000"/>
+      <color theme="1"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+      <sz val="11"/>
       <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="1"/>
     </font>
     <font>
       <b/>
+      <charset val="1"/>
+      <color rgb="FF000000"/>
+      <family val="2"/>
       <sz val="16"/>
-      <color rgb="FF000000"/>
       <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="1"/>
     </font>
     <font>
       <i/>
+      <charset val="1"/>
+      <color rgb="FF000000"/>
+      <family val="2"/>
       <sz val="12"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <charset val="1"/>
       <color rgb="FF000000"/>
+      <family val="2"/>
+      <sz val="12"/>
       <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="1"/>
     </font>
     <font>
       <b/>
+      <charset val="1"/>
+      <color rgb="FF000000"/>
+      <family val="2"/>
       <sz val="12"/>
-      <color rgb="FF000000"/>
       <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="1"/>
     </font>
   </fonts>
   <fills count="3">
@@ -220,136 +208,48 @@
       <diagonal/>
     </border>
     <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top style="medium">
-        <color auto="1"/>
-      </top>
-      <bottom style="medium">
-        <color auto="1"/>
-      </bottom>
+      <left style="medium"/>
+      <right style="medium"/>
+      <top style="medium"/>
+      <bottom style="medium"/>
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="3">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="3">
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Normal 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000006000000}"/>
-    <cellStyle name="Normal 3" xfId="2" xr:uid="{00000000-0005-0000-0000-000007000000}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="FF000000"/>
-      <rgbColor rgb="FFFFFFFF"/>
-      <rgbColor rgb="FFFF0000"/>
-      <rgbColor rgb="FF00FF00"/>
-      <rgbColor rgb="FF0000FF"/>
-      <rgbColor rgb="FFFFFF00"/>
-      <rgbColor rgb="FFFF00FF"/>
-      <rgbColor rgb="FF00FFFF"/>
-      <rgbColor rgb="FF800000"/>
-      <rgbColor rgb="FF008000"/>
-      <rgbColor rgb="FF000080"/>
-      <rgbColor rgb="FF808000"/>
-      <rgbColor rgb="FF800080"/>
-      <rgbColor rgb="FF008080"/>
-      <rgbColor rgb="FFC0C0C0"/>
-      <rgbColor rgb="FF808080"/>
-      <rgbColor rgb="FF9999FF"/>
-      <rgbColor rgb="FF993366"/>
-      <rgbColor rgb="FFFFFFCC"/>
-      <rgbColor rgb="FFCCFFFF"/>
-      <rgbColor rgb="FF660066"/>
-      <rgbColor rgb="FFFF8080"/>
-      <rgbColor rgb="FF0066CC"/>
-      <rgbColor rgb="FFCCCCFF"/>
-      <rgbColor rgb="FF000080"/>
-      <rgbColor rgb="FFFF00FF"/>
-      <rgbColor rgb="FFFFFF00"/>
-      <rgbColor rgb="FF00FFFF"/>
-      <rgbColor rgb="FF800080"/>
-      <rgbColor rgb="FF800000"/>
-      <rgbColor rgb="FF008080"/>
-      <rgbColor rgb="FF0000FF"/>
-      <rgbColor rgb="FF00CCFF"/>
-      <rgbColor rgb="FFCCFFFF"/>
-      <rgbColor rgb="FFCCFFCC"/>
-      <rgbColor rgb="FFFFFF99"/>
-      <rgbColor rgb="FF99CCFF"/>
-      <rgbColor rgb="FFFF99CC"/>
-      <rgbColor rgb="FFCC99FF"/>
-      <rgbColor rgb="FFFFCC99"/>
-      <rgbColor rgb="FF3366FF"/>
-      <rgbColor rgb="FF3CC0DD"/>
-      <rgbColor rgb="FF99CC00"/>
-      <rgbColor rgb="FFFFCC00"/>
-      <rgbColor rgb="FFFF9900"/>
-      <rgbColor rgb="FFFF6600"/>
-      <rgbColor rgb="FF666699"/>
-      <rgbColor rgb="FF969696"/>
-      <rgbColor rgb="FF003366"/>
-      <rgbColor rgb="FF339966"/>
-      <rgbColor rgb="FF003300"/>
-      <rgbColor rgb="FF333300"/>
-      <rgbColor rgb="FF993300"/>
-      <rgbColor rgb="FF993366"/>
-      <rgbColor rgb="FF333399"/>
-      <rgbColor rgb="FF333333"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -677,9 +577,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:K12"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.33203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="16" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.2" defaultColWidth="11.33203125" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="24.5" customWidth="1"/>
     <col min="2" max="2" width="27.5" customWidth="1"/>
@@ -687,132 +587,139 @@
     <col min="4" max="4" width="15.33203125" customWidth="1"/>
     <col min="5" max="5" width="15.1640625" customWidth="1"/>
     <col min="6" max="6" width="43.1640625" customWidth="1"/>
-    <col min="7" max="7" width="16.33203125" customWidth="1"/>
-    <col min="8" max="8" width="17.6640625" customWidth="1"/>
-    <col min="9" max="9" width="15.1640625" customWidth="1"/>
-    <col min="10" max="10" width="53.1640625" customWidth="1"/>
+    <col min="7" max="7" width="25" customWidth="1"/>
+    <col min="8" max="8" width="16.33203125" customWidth="1"/>
+    <col min="9" max="9" width="17.6640625" customWidth="1"/>
+    <col min="10" max="10" width="15.1640625" customWidth="1"/>
+    <col min="11" max="11" width="53.1640625" customWidth="1"/>
     <col min="16384" max="16384" width="9.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="21" x14ac:dyDescent="0.25">
+    <row r="1" ht="21" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" ht="17.25" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>2</v>
       </c>
       <c r="C3" s="2"/>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:11" ht="17" x14ac:dyDescent="0.2">
+    <row r="5" ht="17" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" s="3"/>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:11" s="5" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="4" t="s">
+    <row r="8" spans="1:11" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="B8" s="4" t="s">
+      <c r="B8" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="C8" s="4" t="s">
+      <c r="C8" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="D8" s="4" t="s">
+      <c r="D8" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="E8" s="4" t="s">
+      <c r="E8" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="F8" s="4" t="s">
+      <c r="F8" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="G8" s="4" t="s">
+      <c r="G8" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="H8" s="4" t="s">
+      <c r="H8" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="I8" s="4" t="s">
+      <c r="I8" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="J8" s="4" t="s">
+      <c r="J8" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="K8"/>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="K8" s="5" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E9" s="7" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F9" s="6" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G9" s="6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H9" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="I9" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="J9" s="6" t="s">
+      <c r="I9" s="6" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="J9" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="K9" s="6" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="10" spans="7:11" x14ac:dyDescent="0.25"/>
+    <row r="11" spans="5:11" x14ac:dyDescent="0.25">
       <c r="E11" s="8"/>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="12" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B12" s="9"/>
       <c r="C12" s="9"/>
       <c r="D12" s="9"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:L12"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.33203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="16" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.2" defaultColWidth="11.33203125" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="24.5" customWidth="1"/>
     <col min="2" max="2" width="27.5" customWidth="1"/>
@@ -820,126 +727,133 @@
     <col min="5" max="5" width="33.83203125" customWidth="1"/>
     <col min="6" max="6" width="15.1640625" customWidth="1"/>
     <col min="7" max="7" width="53.1640625" customWidth="1"/>
-    <col min="8" max="8" width="16.33203125" customWidth="1"/>
-    <col min="9" max="9" width="17.6640625" customWidth="1"/>
-    <col min="10" max="10" width="15.1640625" customWidth="1"/>
-    <col min="11" max="11" width="53.1640625" customWidth="1"/>
+    <col min="8" max="8" width="25" customWidth="1"/>
+    <col min="9" max="9" width="16.33203125" customWidth="1"/>
+    <col min="10" max="10" width="17.6640625" customWidth="1"/>
+    <col min="11" max="11" width="15.1640625" customWidth="1"/>
+    <col min="12" max="12" width="53.1640625" customWidth="1"/>
     <col min="16384" max="16384" width="9.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="21" x14ac:dyDescent="0.25">
+    <row r="1" ht="21" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
       <c r="E1" s="1"/>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" ht="17.25" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>2</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" s="2"/>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:12" ht="17" x14ac:dyDescent="0.2">
+    <row r="5" ht="17" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" s="3"/>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:12" s="5" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="4" t="s">
+    <row r="8" spans="1:12" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="B8" s="4" t="s">
+      <c r="B8" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="C8" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="C8" s="4" t="s">
+      <c r="D8" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="D8" s="4" t="s">
+      <c r="E8" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="E8" s="4" t="s">
+      <c r="F8" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="F8" s="4" t="s">
+      <c r="G8" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="G8" s="4" t="s">
+      <c r="H8" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="I8" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="J8" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="H8" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="I8" s="4" t="s">
+      <c r="K8" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="L8" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="J8" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="K8" s="4" t="s">
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A9" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="B9" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C9" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="L8"/>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A9" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="B9" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="C9" s="6" t="s">
+      <c r="D9" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="E9" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="F9" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="G9" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="H9" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="I9" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="J9" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="K9" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="D9" s="6" t="s">
+      <c r="L9" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="E9" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="F9" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="G9" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="H9" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="I9" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="J9" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="K9" s="6" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="10" spans="8:12" x14ac:dyDescent="0.25"/>
+    <row r="11" spans="6:12" x14ac:dyDescent="0.25">
       <c r="F11" s="8"/>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="12" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B12" s="9"/>
       <c r="C12" s="9"/>
       <c r="D12" s="9"/>
@@ -947,6 +861,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
--- a/api/templates/result_notifications/fr.xlsx
+++ b/api/templates/result_notifications/fr.xlsx
@@ -1,14 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
-  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10531"/>
+  <workbookPr filterPrivacy="1" defaultThemeVersion="202300"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B40FDFA3-EC92-8F47-98CD-854E97661189}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" activeTab="1"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet sheetId="1" name="SMS" state="visible" r:id="rId4"/>
-    <sheet sheetId="2" name="Email" state="visible" r:id="rId5"/>
+    <sheet name="SMS" sheetId="1" r:id="rId1"/>
+    <sheet name="Email" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
@@ -140,49 +141,49 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd hh:mm"/>
+    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd\ hh:mm"/>
     <numFmt numFmtId="165" formatCode="m/d/yyyy"/>
   </numFmts>
   <fonts count="5" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
       <color theme="1"/>
+      <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
     </font>
     <font>
       <b/>
+      <sz val="16"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <charset val="1"/>
-      <color rgb="FF000000"/>
-      <family val="2"/>
-      <sz val="16"/>
-      <name val="Calibri"/>
     </font>
     <font>
       <i/>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <charset val="1"/>
-      <color rgb="FF000000"/>
-      <family val="2"/>
-      <sz val="12"/>
-      <name val="Calibri"/>
     </font>
     <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <charset val="1"/>
-      <color rgb="FF000000"/>
-      <family val="2"/>
-      <sz val="12"/>
-      <name val="Calibri"/>
     </font>
     <font>
       <b/>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <charset val="1"/>
-      <color rgb="FF000000"/>
-      <family val="2"/>
-      <sz val="12"/>
-      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="3">
@@ -208,17 +209,33 @@
       <diagonal/>
     </border>
     <border>
-      <left style="medium"/>
-      <right style="medium"/>
-      <top style="medium"/>
-      <bottom style="medium"/>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
@@ -227,23 +244,33 @@
   </cellStyleXfs>
   <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1" shrinkToFit="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+      <alignment wrapText="1" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+      <alignment wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1" shrinkToFit="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -577,17 +604,17 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:K12"/>
-  <sheetFormatPr defaultRowHeight="16" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.2" defaultColWidth="11.33203125" customHeight="1"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.33203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="24.5" customWidth="1"/>
     <col min="2" max="2" width="27.5" customWidth="1"/>
     <col min="3" max="3" width="19.33203125" customWidth="1"/>
     <col min="4" max="4" width="15.33203125" customWidth="1"/>
     <col min="5" max="5" width="15.1640625" customWidth="1"/>
-    <col min="6" max="6" width="43.1640625" customWidth="1"/>
-    <col min="7" max="7" width="25" customWidth="1"/>
+    <col min="6" max="6" width="10.83203125" customWidth="1"/>
+    <col min="7" max="7" width="36.83203125" customWidth="1"/>
     <col min="8" max="8" width="16.33203125" customWidth="1"/>
     <col min="9" max="9" width="17.6640625" customWidth="1"/>
     <col min="10" max="10" width="15.1640625" customWidth="1"/>
@@ -595,78 +622,78 @@
     <col min="16384" max="16384" width="9.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="21" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" ht="17.25" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>2</v>
       </c>
       <c r="C3" s="2"/>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="5" ht="17" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:11" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A6" s="3"/>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:11" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="5" t="s">
+    <row r="8" spans="1:11" s="5" customFormat="1" ht="17" x14ac:dyDescent="0.2">
+      <c r="A8" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="B8" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="C8" s="5" t="s">
+      <c r="C8" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="D8" s="5" t="s">
+      <c r="D8" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E8" s="5" t="s">
+      <c r="E8" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="F8" s="5" t="s">
+      <c r="F8" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="G8" s="5" t="s">
+      <c r="G8" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="H8" s="5" t="s">
+      <c r="H8" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="I8" s="5" t="s">
+      <c r="I8" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="J8" s="5" t="s">
+      <c r="J8" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="K8" s="5" t="s">
+      <c r="K8" s="4" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:11" ht="17" x14ac:dyDescent="0.2">
       <c r="A9" s="6" t="s">
         <v>17</v>
       </c>
@@ -701,41 +728,40 @@
         <v>27</v>
       </c>
     </row>
-    <row r="10" spans="7:11" x14ac:dyDescent="0.25"/>
-    <row r="11" spans="5:11" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="E11" s="8"/>
     </row>
-    <row r="12" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="B12" s="9"/>
       <c r="C12" s="9"/>
       <c r="D12" s="9"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+  <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:L12"/>
-  <sheetFormatPr defaultRowHeight="16" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.2" defaultColWidth="11.33203125" customHeight="1"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.33203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="24.5" customWidth="1"/>
     <col min="2" max="2" width="27.5" customWidth="1"/>
     <col min="3" max="4" width="30.1640625" customWidth="1"/>
     <col min="5" max="5" width="33.83203125" customWidth="1"/>
     <col min="6" max="6" width="15.1640625" customWidth="1"/>
-    <col min="7" max="7" width="53.1640625" customWidth="1"/>
-    <col min="8" max="8" width="25" customWidth="1"/>
-    <col min="9" max="9" width="16.33203125" customWidth="1"/>
+    <col min="7" max="7" width="10.83203125" customWidth="1"/>
+    <col min="8" max="8" width="36.83203125" customWidth="1"/>
+    <col min="9" max="9" width="16.1640625" customWidth="1"/>
     <col min="10" max="10" width="17.6640625" customWidth="1"/>
     <col min="11" max="11" width="15.1640625" customWidth="1"/>
     <col min="12" max="12" width="53.1640625" customWidth="1"/>
     <col min="16384" max="16384" width="9.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="21" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>28</v>
       </c>
@@ -743,75 +769,75 @@
       <c r="D1" s="1"/>
       <c r="E1" s="1"/>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" ht="17.25" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>2</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" s="2"/>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="5" ht="17" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:12" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A6" s="3"/>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:12" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="5" t="s">
+    <row r="8" spans="1:12" s="5" customFormat="1" ht="17" x14ac:dyDescent="0.2">
+      <c r="A8" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="B8" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="C8" s="5" t="s">
+      <c r="C8" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="D8" s="5" t="s">
+      <c r="D8" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="E8" s="5" t="s">
+      <c r="E8" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="F8" s="5" t="s">
+      <c r="F8" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="G8" s="5" t="s">
+      <c r="G8" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="H8" s="5" t="s">
+      <c r="H8" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="I8" s="5" t="s">
+      <c r="I8" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="J8" s="5" t="s">
+      <c r="J8" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="K8" s="5" t="s">
+      <c r="K8" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="L8" s="5" t="s">
+      <c r="L8" s="4" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A9" s="6" t="s">
         <v>17</v>
       </c>
@@ -849,11 +875,10 @@
         <v>27</v>
       </c>
     </row>
-    <row r="10" spans="8:12" x14ac:dyDescent="0.25"/>
-    <row r="11" spans="6:12" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="F11" s="8"/>
     </row>
-    <row r="12" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="B12" s="9"/>
       <c r="C12" s="9"/>
       <c r="D12" s="9"/>
@@ -861,6 +886,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+  <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>